--- a/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR TEMPARATURA OLEO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR TEMPARATURA OLEO.xlsx
@@ -28,25 +28,25 @@
     <t>631430288364</t>
   </si>
   <si>
-    <t>SENSOR TEMP OLEO IRON YS250 FAZER 2006 A 2023/ XTZ250 LANDER 2008 A 2023/ TENERE 352233</t>
+    <t>SENSOR TEMPERATURA  OLEO IRON YS250 FAZER 2006 A 2023/ XTZ250 LANDER 2008 A 2023/ TENERE 352233</t>
   </si>
   <si>
     <t>7909201092940</t>
   </si>
   <si>
-    <t>SENSOR TEMP OLEO IRON CONDOR NEO115</t>
+    <t>SENSOR TEMPERATURA  OLEO IRON CONDOR NEO115</t>
   </si>
   <si>
     <t>7908305618773</t>
   </si>
   <si>
-    <t>SENSOR TEMP OLEO MHX CG TITAN150 2009 A 2015/ FAN160 2016 A 2022/ CACTO150 2016 A 2022/ NMAX160 2017 A 2022/ XRE300 2009 A 2022/ BIZ125/ XRE190</t>
+    <t>SENSOR TEMPERATURA  OLEO MHX CG TITAN150 2009 A 2015/ FAN160 2016 A 2022/ CACTO150 2016 A 2022/ NMAX160 2017 A 2022/ XRE300 2009 A 2022/ BIZ125/ XRE190</t>
   </si>
   <si>
     <t>631430288357</t>
   </si>
   <si>
-    <t>SENSOR TEMP OLEO IRON FAZER YS150 250 2014 A 2024/ XTZ150 CROSSER 2015 A 2023/ YBR125I 2017 A 2023/ FACTOR150 2016 A 2023 352235</t>
+    <t>SENSOR TEMPERATURA  OLEO IRON FAZER YS150 250 2014 A 2024/ XTZ150 CROSSER 2015 A 2023/ YBR125I 2017 A 2023/ FACTOR150 2016 A 2023 352235</t>
   </si>
 </sst>
 </file>
@@ -104,16 +104,16 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -374,10 +374,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>4.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -408,10 +410,10 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>3.0</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>60.0</v>
       </c>
       <c r="E3" s="6"/>
@@ -444,10 +446,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -475,11 +479,13 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="4">
+        <v>50.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
